--- a/course_data_2026/Web_tools/data/lab_results.xlsx
+++ b/course_data_2026/Web_tools/data/lab_results.xlsx
@@ -1,140 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdiazcaballero/Documents/cgps/teaching/cartagena/digitalepiworkshop/hands-on/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8F33254-179A-274C-A181-BA9393072C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="560" windowWidth="30240" windowHeight="18880" xr2:uid="{BA64E9F3-D88C-9C49-A084-22DFE9F308AD}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="560" windowWidth="30240" windowHeight="18880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
-  <si>
-    <t>sample id</t>
-  </si>
-  <si>
-    <t>negative</t>
-  </si>
-  <si>
-    <t>culture</t>
-  </si>
-  <si>
-    <t>123456789-1</t>
-  </si>
-  <si>
-    <t>123456789-2</t>
-  </si>
-  <si>
-    <t>123456789-3</t>
-  </si>
-  <si>
-    <t>123456789-4</t>
-  </si>
-  <si>
-    <t>123456789-5</t>
-  </si>
-  <si>
-    <t>123456789-6</t>
-  </si>
-  <si>
-    <t>123456789-7</t>
-  </si>
-  <si>
-    <t>123456789-8</t>
-  </si>
-  <si>
-    <t>123456789-9</t>
-  </si>
-  <si>
-    <t>123456789-10</t>
-  </si>
-  <si>
-    <t>123456789-11</t>
-  </si>
-  <si>
-    <t>123456789-12</t>
-  </si>
-  <si>
-    <t>123456789-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>K. pneumoniae</t>
-  </si>
-  <si>
-    <t>123456789-14</t>
-  </si>
-  <si>
-    <t>123456789-15</t>
-  </si>
-  <si>
-    <t>123456789-16</t>
-  </si>
-  <si>
-    <t>123456789-17</t>
-  </si>
-  <si>
-    <t>123456789-18</t>
-  </si>
-  <si>
-    <t>123456789-19</t>
-  </si>
-  <si>
-    <t>123456789-20</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,21 +52,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -467,187 +425,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3503FB76-1362-104D-AA2A-0E0738981850}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col width="12.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sample id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>123456789-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>123456789-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>123456789-3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>123456789-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>123456789-5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>123456789-6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>123456789-7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>123456789-8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>123456789-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>K. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>123456789-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>123456789-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K. pneumoniae</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/course_data_2026/Web_tools/data/lab_results.xlsx
+++ b/course_data_2026/Web_tools/data/lab_results.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="12.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>K. pneumoniae</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>K. pneumoniae</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
